--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N28_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>74.09032705510415</v>
+        <v>12.03967814645443</v>
       </c>
       <c r="D2" t="n">
-        <v>74.35442818359924</v>
+        <v>12.08259457983488</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
